--- a/excel_cases/CPU利用率超限定位步骤表.xlsx
+++ b/excel_cases/CPU利用率超限定位步骤表.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -515,6 +515,35 @@
 依据：R23.0未EOS</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -555,6 +584,35 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -595,6 +653,35 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -636,6 +723,35 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -676,6 +792,35 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -727,6 +872,35 @@
           <t>告警消除</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -779,6 +953,35 @@
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -831,6 +1034,35 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -876,6 +1108,35 @@
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
